--- a/data/nzd0022/nzd0022.xlsx
+++ b/data/nzd0022/nzd0022.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I419"/>
+  <dimension ref="A1:I423"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14263,6 +14263,138 @@
         <v>376.91</v>
       </c>
       <c r="I419" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-25 22:10:44+00:00</t>
+        </is>
+      </c>
+      <c r="B420" t="n">
+        <v>388.07</v>
+      </c>
+      <c r="C420" t="n">
+        <v>377.35</v>
+      </c>
+      <c r="D420" t="n">
+        <v>385.85</v>
+      </c>
+      <c r="E420" t="n">
+        <v>382.13</v>
+      </c>
+      <c r="F420" t="n">
+        <v>385.77</v>
+      </c>
+      <c r="G420" t="n">
+        <v>387.22</v>
+      </c>
+      <c r="H420" t="n">
+        <v>374.63</v>
+      </c>
+      <c r="I420" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-03 22:10:55+00:00</t>
+        </is>
+      </c>
+      <c r="B421" t="n">
+        <v>389.07</v>
+      </c>
+      <c r="C421" t="n">
+        <v>379.53</v>
+      </c>
+      <c r="D421" t="n">
+        <v>386.82</v>
+      </c>
+      <c r="E421" t="n">
+        <v>382.72</v>
+      </c>
+      <c r="F421" t="n">
+        <v>384.17</v>
+      </c>
+      <c r="G421" t="n">
+        <v>385.02</v>
+      </c>
+      <c r="H421" t="n">
+        <v>372.06</v>
+      </c>
+      <c r="I421" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-10 22:17:07+00:00</t>
+        </is>
+      </c>
+      <c r="B422" t="n">
+        <v>389.46</v>
+      </c>
+      <c r="C422" t="n">
+        <v>376.43</v>
+      </c>
+      <c r="D422" t="n">
+        <v>386.93</v>
+      </c>
+      <c r="E422" t="n">
+        <v>382.52</v>
+      </c>
+      <c r="F422" t="n">
+        <v>383.82</v>
+      </c>
+      <c r="G422" t="n">
+        <v>385.11</v>
+      </c>
+      <c r="H422" t="n">
+        <v>372.65</v>
+      </c>
+      <c r="I422" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-19 22:11:05+00:00</t>
+        </is>
+      </c>
+      <c r="B423" t="n">
+        <v>389.05</v>
+      </c>
+      <c r="C423" t="n">
+        <v>376.74</v>
+      </c>
+      <c r="D423" t="n">
+        <v>387.47</v>
+      </c>
+      <c r="E423" t="n">
+        <v>382.29</v>
+      </c>
+      <c r="F423" t="n">
+        <v>383.36</v>
+      </c>
+      <c r="G423" t="n">
+        <v>384.58</v>
+      </c>
+      <c r="H423" t="n">
+        <v>371.92</v>
+      </c>
+      <c r="I423" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -14279,7 +14411,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B480"/>
+  <dimension ref="A1:B484"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19082,6 +19214,46 @@
       </c>
       <c r="B480" t="n">
         <v>0.9</v>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>2026-06-25 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B481" t="n">
+        <v>-0.71</v>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>2026-07-03 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B482" t="n">
+        <v>0.62</v>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>2026-07-10 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B483" t="n">
+        <v>-0.92</v>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>2026-07-19 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B484" t="n">
+        <v>0.41</v>
       </c>
     </row>
   </sheetData>
@@ -19250,28 +19422,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>0.204609636195829</v>
+        <v>0.2055510807304516</v>
       </c>
       <c r="J2" t="n">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="K2" t="n">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1122595716489393</v>
+        <v>0.1155394165942453</v>
       </c>
       <c r="M2" t="n">
-        <v>3.66519843414902</v>
+        <v>3.636555992782695</v>
       </c>
       <c r="N2" t="n">
-        <v>20.11103197019658</v>
+        <v>19.92514592768326</v>
       </c>
       <c r="O2" t="n">
-        <v>4.484532525269114</v>
+        <v>4.463759169991506</v>
       </c>
       <c r="P2" t="n">
-        <v>382.9111106802474</v>
+        <v>382.9020536198624</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -19328,28 +19500,28 @@
         <v>0.0684</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1740130193518623</v>
+        <v>0.1809708972837489</v>
       </c>
       <c r="J3" t="n">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="K3" t="n">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="L3" t="n">
-        <v>0.07841920908406974</v>
+        <v>0.08560421643334948</v>
       </c>
       <c r="M3" t="n">
-        <v>3.64532905266828</v>
+        <v>3.649325664554026</v>
       </c>
       <c r="N3" t="n">
-        <v>21.61692987788247</v>
+        <v>21.5511379461226</v>
       </c>
       <c r="O3" t="n">
-        <v>4.649401023560182</v>
+        <v>4.642320319207045</v>
       </c>
       <c r="P3" t="n">
-        <v>369.1411683060358</v>
+        <v>369.0742898128591</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -19406,28 +19578,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>0.06862223332297311</v>
+        <v>0.08003689659349637</v>
       </c>
       <c r="J4" t="n">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="K4" t="n">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="L4" t="n">
-        <v>0.02503260094069082</v>
+        <v>0.03352841815908247</v>
       </c>
       <c r="M4" t="n">
-        <v>2.565873902361032</v>
+        <v>2.601084765747888</v>
       </c>
       <c r="N4" t="n">
-        <v>11.14123632782426</v>
+        <v>11.37549161152107</v>
       </c>
       <c r="O4" t="n">
-        <v>3.337849057076167</v>
+        <v>3.372757271361382</v>
       </c>
       <c r="P4" t="n">
-        <v>378.8624767083941</v>
+        <v>378.7527332871383</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -19484,28 +19656,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>0.02547181286998362</v>
+        <v>0.02621287504142993</v>
       </c>
       <c r="J5" t="n">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="K5" t="n">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="L5" t="n">
-        <v>0.005944781848045588</v>
+        <v>0.006440640329966274</v>
       </c>
       <c r="M5" t="n">
-        <v>1.949324115153063</v>
+        <v>1.93417278729345</v>
       </c>
       <c r="N5" t="n">
-        <v>6.605893881162694</v>
+        <v>6.545026435072161</v>
       </c>
       <c r="O5" t="n">
-        <v>2.570193354820351</v>
+        <v>2.558324927579013</v>
       </c>
       <c r="P5" t="n">
-        <v>381.3340925406123</v>
+        <v>381.326975269017</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -19562,28 +19734,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>0.09713824659119592</v>
+        <v>0.091891157797708</v>
       </c>
       <c r="J6" t="n">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="K6" t="n">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0397591007309287</v>
+        <v>0.03634775261779255</v>
       </c>
       <c r="M6" t="n">
-        <v>2.920709522312086</v>
+        <v>2.915603172203254</v>
       </c>
       <c r="N6" t="n">
-        <v>13.87590958137817</v>
+        <v>13.82316655597291</v>
       </c>
       <c r="O6" t="n">
-        <v>3.72503819864685</v>
+        <v>3.717951930293466</v>
       </c>
       <c r="P6" t="n">
-        <v>384.4515390030206</v>
+        <v>384.501945063208</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -19640,28 +19812,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1160519579987899</v>
+        <v>0.1006417060004849</v>
       </c>
       <c r="J7" t="n">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="K7" t="n">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="L7" t="n">
-        <v>0.04202514953963588</v>
+        <v>0.03164140927770709</v>
       </c>
       <c r="M7" t="n">
-        <v>3.420659722887504</v>
+        <v>3.463836906210073</v>
       </c>
       <c r="N7" t="n">
-        <v>18.64959293826699</v>
+        <v>19.09633568616279</v>
       </c>
       <c r="O7" t="n">
-        <v>4.318517446794327</v>
+        <v>4.369935432722409</v>
       </c>
       <c r="P7" t="n">
-        <v>390.5416433824174</v>
+        <v>390.689803786584</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -19718,28 +19890,28 @@
         <v>0.2</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1134035405065475</v>
+        <v>-0.1323464221971585</v>
       </c>
       <c r="J8" t="n">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="K8" t="n">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0172359227976604</v>
+        <v>0.02338683804995267</v>
       </c>
       <c r="M8" t="n">
-        <v>5.158616292807838</v>
+        <v>5.200850489256088</v>
       </c>
       <c r="N8" t="n">
-        <v>44.54382761491742</v>
+        <v>45.05978801408289</v>
       </c>
       <c r="O8" t="n">
-        <v>6.674116242238925</v>
+        <v>6.712658788742572</v>
       </c>
       <c r="P8" t="n">
-        <v>385.918300925764</v>
+        <v>386.1004210143968</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -19777,7 +19949,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I419"/>
+  <dimension ref="A1:I423"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39465,6 +39637,194 @@
         </is>
       </c>
     </row>
+    <row r="420">
+      <c r="A420" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-25 22:10:44+00:00</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>-34.81159653644908,173.38645813731176</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>-34.8110585020932,173.3870854849751</t>
+        </is>
+      </c>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>-34.8104912504888,173.3876259440489</t>
+        </is>
+      </c>
+      <c r="E420" t="inlineStr">
+        <is>
+          <t>-34.80990928486705,173.3881084689358</t>
+        </is>
+      </c>
+      <c r="F420" t="inlineStr">
+        <is>
+          <t>-34.80926638755369,173.38850778221567</t>
+        </is>
+      </c>
+      <c r="G420" t="inlineStr">
+        <is>
+          <t>-34.80862921026625,173.38883363897753</t>
+        </is>
+      </c>
+      <c r="H420" t="inlineStr">
+        <is>
+          <t>-34.807956219661286,173.3891162876871</t>
+        </is>
+      </c>
+      <c r="I420" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-03 22:10:55+00:00</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>-34.81159121724706,173.3864493085022</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>-34.8110458683529,173.38706722391237</t>
+        </is>
+      </c>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>-34.81048591308184,173.38761754191557</t>
+        </is>
+      </c>
+      <c r="E421" t="inlineStr">
+        <is>
+          <t>-34.809906595789634,173.3881029028763</t>
+        </is>
+      </c>
+      <c r="F421" t="inlineStr">
+        <is>
+          <t>-34.80927281376502,173.38852344444612</t>
+        </is>
+      </c>
+      <c r="G421" t="inlineStr">
+        <is>
+          <t>-34.8086348906063,173.3888566848449</t>
+        </is>
+      </c>
+      <c r="H421" t="inlineStr">
+        <is>
+          <t>-34.8079601661433,173.38914397523726</t>
+        </is>
+      </c>
+      <c r="I421" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-10 22:17:07+00:00</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>-34.8115891427581,173.38644586526675</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>-34.81106383376258,173.38709319148032</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>-34.810485307808854,173.3876165890964</t>
+        </is>
+      </c>
+      <c r="E422" t="inlineStr">
+        <is>
+          <t>-34.80990750734132,173.3881047896761</t>
+        </is>
+      </c>
+      <c r="F422" t="inlineStr">
+        <is>
+          <t>-34.80927421949846,173.38852687055933</t>
+        </is>
+      </c>
+      <c r="G422" t="inlineStr">
+        <is>
+          <t>-34.80863465822884,173.38885574205938</t>
+        </is>
+      </c>
+      <c r="H422" t="inlineStr">
+        <is>
+          <t>-34.80795926014215,173.3891376189512</t>
+        </is>
+      </c>
+      <c r="I422" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-19 22:11:05+00:00</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>-34.81159132363111,173.38644948507837</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>-34.81106203722187,173.38709059472302</t>
+        </is>
+      </c>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>-34.810482336468596,173.38761191162067</t>
+        </is>
+      </c>
+      <c r="E423" t="inlineStr">
+        <is>
+          <t>-34.80990855562574,173.3881069594959</t>
+        </is>
+      </c>
+      <c r="F423" t="inlineStr">
+        <is>
+          <t>-34.80927606703372,173.3885313734512</t>
+        </is>
+      </c>
+      <c r="G423" t="inlineStr">
+        <is>
+          <t>-34.80863602667378,173.38886129401874</t>
+        </is>
+      </c>
+      <c r="H423" t="inlineStr">
+        <is>
+          <t>-34.80796038112657,173.38914548350854</t>
+        </is>
+      </c>
+      <c r="I423" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0022/nzd0022.xlsx
+++ b/data/nzd0022/nzd0022.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I423"/>
+  <dimension ref="A1:I426"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14397,6 +14397,105 @@
       <c r="I423" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-03 22:17:14+00:00</t>
+        </is>
+      </c>
+      <c r="B424" t="n">
+        <v>388.89</v>
+      </c>
+      <c r="C424" t="n">
+        <v>378.33</v>
+      </c>
+      <c r="D424" t="n">
+        <v>387.14</v>
+      </c>
+      <c r="E424" t="n">
+        <v>382.67</v>
+      </c>
+      <c r="F424" t="n">
+        <v>383.31</v>
+      </c>
+      <c r="G424" t="n">
+        <v>384.75</v>
+      </c>
+      <c r="H424" t="n">
+        <v>372.7</v>
+      </c>
+      <c r="I424" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B425" t="n">
+        <v>389.05</v>
+      </c>
+      <c r="C425" t="n">
+        <v>378.78</v>
+      </c>
+      <c r="D425" t="n">
+        <v>387.31</v>
+      </c>
+      <c r="E425" t="n">
+        <v>383.18</v>
+      </c>
+      <c r="F425" t="n">
+        <v>383.23</v>
+      </c>
+      <c r="G425" t="n">
+        <v>385.63</v>
+      </c>
+      <c r="H425" t="n">
+        <v>373.17</v>
+      </c>
+      <c r="I425" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:17:20+00:00</t>
+        </is>
+      </c>
+      <c r="B426" t="n">
+        <v>390.19</v>
+      </c>
+      <c r="C426" t="n">
+        <v>379.5</v>
+      </c>
+      <c r="D426" t="n">
+        <v>387.53</v>
+      </c>
+      <c r="E426" t="n">
+        <v>383.37</v>
+      </c>
+      <c r="F426" t="n">
+        <v>384.04</v>
+      </c>
+      <c r="G426" t="n">
+        <v>385.39</v>
+      </c>
+      <c r="H426" t="n">
+        <v>373.19</v>
+      </c>
+      <c r="I426" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -14411,7 +14510,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B484"/>
+  <dimension ref="A1:B487"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19254,6 +19353,36 @@
       </c>
       <c r="B484" t="n">
         <v>0.41</v>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>2026-08-03 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B485" t="n">
+        <v>0.63</v>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B486" t="n">
+        <v>0.36</v>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B487" t="n">
+        <v>0.04</v>
       </c>
     </row>
   </sheetData>
@@ -19422,28 +19551,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2055510807304516</v>
+        <v>0.2068383442215515</v>
       </c>
       <c r="J2" t="n">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="K2" t="n">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1155394165942453</v>
+        <v>0.1185723259503368</v>
       </c>
       <c r="M2" t="n">
-        <v>3.636555992782695</v>
+        <v>3.616984599291642</v>
       </c>
       <c r="N2" t="n">
-        <v>19.92514592768326</v>
+        <v>19.79273393763929</v>
       </c>
       <c r="O2" t="n">
-        <v>4.463759169991506</v>
+        <v>4.448902554298002</v>
       </c>
       <c r="P2" t="n">
-        <v>382.9020536198624</v>
+        <v>382.8896247635786</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -19500,28 +19629,28 @@
         <v>0.0684</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1809708972837489</v>
+        <v>0.1877971531268681</v>
       </c>
       <c r="J3" t="n">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="K3" t="n">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="L3" t="n">
-        <v>0.08560421643334948</v>
+        <v>0.09237125074509667</v>
       </c>
       <c r="M3" t="n">
-        <v>3.649325664554026</v>
+        <v>3.661208658195016</v>
       </c>
       <c r="N3" t="n">
-        <v>21.5511379461226</v>
+        <v>21.56700144268486</v>
       </c>
       <c r="O3" t="n">
-        <v>4.642320319207045</v>
+        <v>4.644028579012501</v>
       </c>
       <c r="P3" t="n">
-        <v>369.0742898128591</v>
+        <v>369.0084104757871</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -19578,28 +19707,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>0.08003689659349637</v>
+        <v>0.0889434366182294</v>
       </c>
       <c r="J4" t="n">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="K4" t="n">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="L4" t="n">
-        <v>0.03352841815908247</v>
+        <v>0.04078732901930426</v>
       </c>
       <c r="M4" t="n">
-        <v>2.601084765747888</v>
+        <v>2.630787652622514</v>
       </c>
       <c r="N4" t="n">
-        <v>11.37549161152107</v>
+        <v>11.57864640736104</v>
       </c>
       <c r="O4" t="n">
-        <v>3.372757271361382</v>
+        <v>3.402741013853543</v>
       </c>
       <c r="P4" t="n">
-        <v>378.7527332871383</v>
+        <v>378.6667825452373</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -19656,28 +19785,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>0.02621287504142993</v>
+        <v>0.02765725324153143</v>
       </c>
       <c r="J5" t="n">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="K5" t="n">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="L5" t="n">
-        <v>0.006440640329966274</v>
+        <v>0.007279655051806388</v>
       </c>
       <c r="M5" t="n">
-        <v>1.93417278729345</v>
+        <v>1.927170020418258</v>
       </c>
       <c r="N5" t="n">
-        <v>6.545026435072161</v>
+        <v>6.506802667205919</v>
       </c>
       <c r="O5" t="n">
-        <v>2.558324927579013</v>
+        <v>2.550843520721316</v>
       </c>
       <c r="P5" t="n">
-        <v>381.326975269017</v>
+        <v>381.313048414566</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -19734,28 +19863,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>0.091891157797708</v>
+        <v>0.08709559659598451</v>
       </c>
       <c r="J6" t="n">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="K6" t="n">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03634775261779255</v>
+        <v>0.03313152797142671</v>
       </c>
       <c r="M6" t="n">
-        <v>2.915603172203254</v>
+        <v>2.916225258828573</v>
       </c>
       <c r="N6" t="n">
-        <v>13.82316655597291</v>
+        <v>13.80866685122338</v>
       </c>
       <c r="O6" t="n">
-        <v>3.717951930293466</v>
+        <v>3.716001460067444</v>
       </c>
       <c r="P6" t="n">
-        <v>384.501945063208</v>
+        <v>384.5481717186698</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -19812,28 +19941,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1006417060004849</v>
+        <v>0.0893218770779408</v>
       </c>
       <c r="J7" t="n">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="K7" t="n">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="L7" t="n">
-        <v>0.03164140927770709</v>
+        <v>0.02493095038262383</v>
       </c>
       <c r="M7" t="n">
-        <v>3.463836906210073</v>
+        <v>3.497315524435205</v>
       </c>
       <c r="N7" t="n">
-        <v>19.09633568616279</v>
+        <v>19.42014902500681</v>
       </c>
       <c r="O7" t="n">
-        <v>4.369935432722409</v>
+        <v>4.406829815752682</v>
       </c>
       <c r="P7" t="n">
-        <v>390.689803786584</v>
+        <v>390.7990400304053</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -19890,28 +20019,28 @@
         <v>0.2</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1323464221971585</v>
+        <v>-0.1455512133215863</v>
       </c>
       <c r="J8" t="n">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="K8" t="n">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="L8" t="n">
-        <v>0.02338683804995267</v>
+        <v>0.0282429717663939</v>
       </c>
       <c r="M8" t="n">
-        <v>5.200850489256088</v>
+        <v>5.229723374776877</v>
       </c>
       <c r="N8" t="n">
-        <v>45.05978801408289</v>
+        <v>45.36483103987656</v>
       </c>
       <c r="O8" t="n">
-        <v>6.712658788742572</v>
+        <v>6.735341939343284</v>
       </c>
       <c r="P8" t="n">
-        <v>386.1004210143968</v>
+        <v>386.2278471284592</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -19949,7 +20078,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I423"/>
+  <dimension ref="A1:I426"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39825,6 +39954,147 @@
         </is>
       </c>
     </row>
+    <row r="424">
+      <c r="A424" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-03 22:17:14+00:00</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>-34.81159217470348,173.38645089768784</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>-34.811052822705705,173.38707727587283</t>
+        </is>
+      </c>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>-34.810484152287664,173.387614770078</t>
+        </is>
+      </c>
+      <c r="E424" t="inlineStr">
+        <is>
+          <t>-34.80990682367756,173.38810337457625</t>
+        </is>
+      </c>
+      <c r="F424" t="inlineStr">
+        <is>
+          <t>-34.809276267852766,173.38853186289597</t>
+        </is>
+      </c>
+      <c r="G424" t="inlineStr">
+        <is>
+          <t>-34.80863558773864,173.38885951320157</t>
+        </is>
+      </c>
+      <c r="H424" t="inlineStr">
+        <is>
+          <t>-34.80795918336237,173.38913708028286</t>
+        </is>
+      </c>
+      <c r="I424" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>-34.81159132363111,173.38644948507837</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>-34.811050214823496,173.38707350638745</t>
+        </is>
+      </c>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>-34.81048321686573,173.38761329753933</t>
+        </is>
+      </c>
+      <c r="E425" t="inlineStr">
+        <is>
+          <t>-34.809904499220615,173.38809856323695</t>
+        </is>
+      </c>
+      <c r="F425" t="inlineStr">
+        <is>
+          <t>-34.809276589163225,173.38853264600763</t>
+        </is>
+      </c>
+      <c r="G425" t="inlineStr">
+        <is>
+          <t>-34.80863331560336,173.3888502948541</t>
+        </is>
+      </c>
+      <c r="H425" t="inlineStr">
+        <is>
+          <t>-34.80795846163239,173.38913201680086</t>
+        </is>
+      </c>
+      <c r="I425" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:17:20+00:00</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>-34.811585259740035,173.3864394202368</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>-34.811046042211714,173.38706747521138</t>
+        </is>
+      </c>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>-34.81048200631967,173.38761139190112</t>
+        </is>
+      </c>
+      <c r="E426" t="inlineStr">
+        <is>
+          <t>-34.80990363324641,173.3880967707773</t>
+        </is>
+      </c>
+      <c r="F426" t="inlineStr">
+        <is>
+          <t>-34.8092733358946,173.38852471700244</t>
+        </is>
+      </c>
+      <c r="G426" t="inlineStr">
+        <is>
+          <t>-34.808633935276696,173.3888528089488</t>
+        </is>
+      </c>
+      <c r="H426" t="inlineStr">
+        <is>
+          <t>-34.807958430920465,173.38913180133355</t>
+        </is>
+      </c>
+      <c r="I426" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0022/nzd0022.xlsx
+++ b/data/nzd0022/nzd0022.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I426"/>
+  <dimension ref="A1:I428"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14496,6 +14496,72 @@
       <c r="I426" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-04 22:17:25+00:00</t>
+        </is>
+      </c>
+      <c r="B427" t="n">
+        <v>390.04</v>
+      </c>
+      <c r="C427" t="n">
+        <v>378.89</v>
+      </c>
+      <c r="D427" t="n">
+        <v>386.47</v>
+      </c>
+      <c r="E427" t="n">
+        <v>382.48</v>
+      </c>
+      <c r="F427" t="n">
+        <v>382.76</v>
+      </c>
+      <c r="G427" t="n">
+        <v>384.2</v>
+      </c>
+      <c r="H427" t="n">
+        <v>371.97</v>
+      </c>
+      <c r="I427" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-28 22:17:40+00:00</t>
+        </is>
+      </c>
+      <c r="B428" t="n">
+        <v>388.57</v>
+      </c>
+      <c r="C428" t="n">
+        <v>378.66</v>
+      </c>
+      <c r="D428" t="n">
+        <v>385.98</v>
+      </c>
+      <c r="E428" t="n">
+        <v>382.09</v>
+      </c>
+      <c r="F428" t="n">
+        <v>382.31</v>
+      </c>
+      <c r="G428" t="n">
+        <v>383.94</v>
+      </c>
+      <c r="H428" t="n">
+        <v>372.57</v>
+      </c>
+      <c r="I428" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -14510,7 +14576,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B487"/>
+  <dimension ref="A1:B489"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19383,6 +19449,26 @@
       </c>
       <c r="B487" t="n">
         <v>0.04</v>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="inlineStr">
+        <is>
+          <t>2026-09-04 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B488" t="n">
+        <v>-0.15</v>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>2026-09-28 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B489" t="n">
+        <v>0.8</v>
       </c>
     </row>
   </sheetData>
@@ -19551,28 +19637,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2068383442215515</v>
+        <v>0.2075837363953827</v>
       </c>
       <c r="J2" t="n">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="K2" t="n">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1185723259503368</v>
+        <v>0.1205008262348101</v>
       </c>
       <c r="M2" t="n">
-        <v>3.616984599291642</v>
+        <v>3.603552166000226</v>
       </c>
       <c r="N2" t="n">
-        <v>19.79273393763929</v>
+        <v>19.70563878208476</v>
       </c>
       <c r="O2" t="n">
-        <v>4.448902554298002</v>
+        <v>4.439103375917794</v>
       </c>
       <c r="P2" t="n">
-        <v>382.8896247635786</v>
+        <v>382.882408717737</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -19629,28 +19715,28 @@
         <v>0.0684</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1877971531268681</v>
+        <v>0.1920987999895986</v>
       </c>
       <c r="J3" t="n">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="K3" t="n">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="L3" t="n">
-        <v>0.09237125074509667</v>
+        <v>0.0968252231344241</v>
       </c>
       <c r="M3" t="n">
-        <v>3.661208658195016</v>
+        <v>3.667816464648427</v>
       </c>
       <c r="N3" t="n">
-        <v>21.56700144268486</v>
+        <v>21.56706537636281</v>
       </c>
       <c r="O3" t="n">
-        <v>4.644028579012501</v>
+        <v>4.644035462435963</v>
       </c>
       <c r="P3" t="n">
-        <v>369.0084104757871</v>
+        <v>368.9667148581079</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -19707,28 +19793,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0889434366182294</v>
+        <v>0.09367746995408505</v>
       </c>
       <c r="J4" t="n">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="K4" t="n">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="L4" t="n">
-        <v>0.04078732901930426</v>
+        <v>0.04507959328589028</v>
       </c>
       <c r="M4" t="n">
-        <v>2.630787652622514</v>
+        <v>2.64392420644819</v>
       </c>
       <c r="N4" t="n">
-        <v>11.57864640736104</v>
+        <v>11.64705021272908</v>
       </c>
       <c r="O4" t="n">
-        <v>3.402741013853543</v>
+        <v>3.412777492414219</v>
       </c>
       <c r="P4" t="n">
-        <v>378.6667825452373</v>
+        <v>378.6208972381881</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -19785,28 +19871,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>0.02765725324153143</v>
+        <v>0.02786112663762801</v>
       </c>
       <c r="J5" t="n">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="K5" t="n">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="L5" t="n">
-        <v>0.007279655051806388</v>
+        <v>0.007470234502585438</v>
       </c>
       <c r="M5" t="n">
-        <v>1.927170020418258</v>
+        <v>1.919057068975631</v>
       </c>
       <c r="N5" t="n">
-        <v>6.506802667205919</v>
+        <v>6.476660617877343</v>
       </c>
       <c r="O5" t="n">
-        <v>2.550843520721316</v>
+        <v>2.54492841114978</v>
       </c>
       <c r="P5" t="n">
-        <v>381.313048414566</v>
+        <v>381.3110766200666</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -19863,28 +19949,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>0.08709559659598451</v>
+        <v>0.08307607628100515</v>
       </c>
       <c r="J6" t="n">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="K6" t="n">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03313152797142671</v>
+        <v>0.03038068901951374</v>
       </c>
       <c r="M6" t="n">
-        <v>2.916225258828573</v>
+        <v>2.920305760235842</v>
       </c>
       <c r="N6" t="n">
-        <v>13.80866685122338</v>
+        <v>13.83248082964206</v>
       </c>
       <c r="O6" t="n">
-        <v>3.716001460067444</v>
+        <v>3.71920432749292</v>
       </c>
       <c r="P6" t="n">
-        <v>384.5481717186698</v>
+        <v>384.5870981689961</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -19941,28 +20027,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0893218770779408</v>
+        <v>0.08091908962434376</v>
       </c>
       <c r="J7" t="n">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="K7" t="n">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02493095038262383</v>
+        <v>0.0203857707096976</v>
       </c>
       <c r="M7" t="n">
-        <v>3.497315524435205</v>
+        <v>3.525503063312766</v>
       </c>
       <c r="N7" t="n">
-        <v>19.42014902500681</v>
+        <v>19.71461875103421</v>
       </c>
       <c r="O7" t="n">
-        <v>4.406829815752682</v>
+        <v>4.440114722733434</v>
       </c>
       <c r="P7" t="n">
-        <v>390.7990400304053</v>
+        <v>390.8804923953984</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -20019,28 +20105,28 @@
         <v>0.2</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1455512133215863</v>
+        <v>-0.1547533292778023</v>
       </c>
       <c r="J8" t="n">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="K8" t="n">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0282429717663939</v>
+        <v>0.03184741023712045</v>
       </c>
       <c r="M8" t="n">
-        <v>5.229723374776877</v>
+        <v>5.253182233738132</v>
       </c>
       <c r="N8" t="n">
-        <v>45.36483103987656</v>
+        <v>45.61504926741079</v>
       </c>
       <c r="O8" t="n">
-        <v>6.735341939343284</v>
+        <v>6.753891416613891</v>
       </c>
       <c r="P8" t="n">
-        <v>386.2278471284592</v>
+        <v>386.3170421297926</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -20078,7 +20164,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I426"/>
+  <dimension ref="A1:I428"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40095,6 +40181,100 @@
         </is>
       </c>
     </row>
+    <row r="427">
+      <c r="A427" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-04 22:17:25+00:00</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>-34.81158605762049,173.38644074455797</t>
+        </is>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>-34.811049577341166,173.38707258495774</t>
+        </is>
+      </c>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>-34.81048783895041,173.38762057361305</t>
+        </is>
+      </c>
+      <c r="E427" t="inlineStr">
+        <is>
+          <t>-34.809907689651666,173.38810516703606</t>
+        </is>
+      </c>
+      <c r="F427" t="inlineStr">
+        <is>
+          <t>-34.80927847686206,173.3885372467887</t>
+        </is>
+      </c>
+      <c r="G427" t="inlineStr">
+        <is>
+          <t>-34.80863700782284,173.388865274669</t>
+        </is>
+      </c>
+      <c r="H427" t="inlineStr">
+        <is>
+          <t>-34.80796030434683,173.38914494484024</t>
+        </is>
+      </c>
+      <c r="I427" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-28 22:17:40+00:00</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>-34.81159387684815,173.38645372290685</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>-34.811050910258764,173.38707451158353</t>
+        </is>
+      </c>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>-34.81049053516626,173.38762481798975</t>
+        </is>
+      </c>
+      <c r="E428" t="inlineStr">
+        <is>
+          <t>-34.809909467177384,173.38810884629575</t>
+        </is>
+      </c>
+      <c r="F428" t="inlineStr">
+        <is>
+          <t>-34.809280284233125,173.38854165179205</t>
+        </is>
+      </c>
+      <c r="G428" t="inlineStr">
+        <is>
+          <t>-34.80863767913526,173.38886799827188</t>
+        </is>
+      </c>
+      <c r="H428" t="inlineStr">
+        <is>
+          <t>-34.80795938298977,173.3891384808205</t>
+        </is>
+      </c>
+      <c r="I428" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
